--- a/server/data/plan-docs/OptimylHealthStandardPlanBenefits.xlsx
+++ b/server/data/plan-docs/OptimylHealthStandardPlanBenefits.xlsx
@@ -450,7 +450,7 @@
         <v>OPTIMYL-1</v>
       </c>
       <c r="B2" t="str">
-        <v>OPTIMYL RBP 1500 7000</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C2" t="str">
         <v>RBP</v>
@@ -479,7 +479,7 @@
         <v>OPTIMYL-2</v>
       </c>
       <c r="B3" t="str">
-        <v>OPTIMYL RBP 2500 7000</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C3" t="str">
         <v>RBP</v>
@@ -508,7 +508,7 @@
         <v>OPTIMYL-3</v>
       </c>
       <c r="B4" t="str">
-        <v>OPTIMYL RBP 3500 7000</v>
+        <v>OPTIMYL PLAN 3</v>
       </c>
       <c r="C4" t="str">
         <v>RBP</v>
@@ -537,7 +537,7 @@
         <v>OPTIMYL-4</v>
       </c>
       <c r="B5" t="str">
-        <v>OPTIMYL RBP 4500 9000</v>
+        <v>OPTIMYL PLAN 4</v>
       </c>
       <c r="C5" t="str">
         <v>RBP</v>
@@ -570,7 +570,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -606,7 +606,7 @@
         <v>OPTIMYL-1</v>
       </c>
       <c r="B2" t="str">
-        <v>OPTIMYL RBP 1500 7000</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -632,7 +632,7 @@
         <v>OPTIMYL-1</v>
       </c>
       <c r="B3" t="str">
-        <v>OPTIMYL RBP 1500 7000</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -658,7 +658,7 @@
         <v>OPTIMYL-1</v>
       </c>
       <c r="B4" t="str">
-        <v>OPTIMYL RBP 1500 7000</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -684,7 +684,7 @@
         <v>OPTIMYL-1</v>
       </c>
       <c r="B5" t="str">
-        <v>OPTIMYL RBP 1500 7000</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -696,7 +696,7 @@
         <v>Ded &amp; coins</v>
       </c>
       <c r="G5">
-        <v>0.2</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H5" t="str">
         <v>Yes</v>
@@ -710,7 +710,7 @@
         <v>OPTIMYL-1</v>
       </c>
       <c r="B6" t="str">
-        <v>OPTIMYL RBP 1500 7000</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -722,7 +722,7 @@
         <v>Ded &amp; coins</v>
       </c>
       <c r="G6">
-        <v>0.2</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H6" t="str">
         <v>Yes</v>
@@ -736,22 +736,22 @@
         <v>OPTIMYL-1</v>
       </c>
       <c r="B7" t="str">
-        <v>OPTIMYL RBP 1500 7000</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7" t="str">
-        <v>Tier 1 Rx (Generic)</v>
+        <v>Inpatient Facility</v>
       </c>
       <c r="E7" t="str">
-        <v>$15.00</v>
-      </c>
-      <c r="F7">
-        <v>15</v>
+        <v>Ded &amp; coins</v>
+      </c>
+      <c r="G7">
+        <v>0.19999999999999996</v>
       </c>
       <c r="H7" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -762,19 +762,19 @@
         <v>OPTIMYL-1</v>
       </c>
       <c r="B8" t="str">
-        <v>OPTIMYL RBP 1500 7000</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C8">
         <v>7</v>
       </c>
       <c r="D8" t="str">
-        <v>Tier 2 Rx (Preferred Brand)</v>
+        <v>Tier 1 Rx (Generic)</v>
       </c>
       <c r="E8" t="str">
-        <v>$45.00</v>
+        <v>$15.00</v>
       </c>
       <c r="F8">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="H8" t="str">
         <v>No</v>
@@ -788,19 +788,19 @@
         <v>OPTIMYL-1</v>
       </c>
       <c r="B9" t="str">
-        <v>OPTIMYL RBP 1500 7000</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9" t="str">
-        <v>Tier 3 Rx (Non-Preferred Brand)</v>
+        <v>Tier 2 Rx (Preferred Brand)</v>
       </c>
       <c r="E9" t="str">
-        <v>$75.00</v>
+        <v>$45.00</v>
       </c>
       <c r="F9">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="H9" t="str">
         <v>No</v>
@@ -814,16 +814,19 @@
         <v>OPTIMYL-1</v>
       </c>
       <c r="B10" t="str">
-        <v>OPTIMYL RBP 1500 7000</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C10">
         <v>9</v>
       </c>
       <c r="D10" t="str">
-        <v>Tier 4 Rx (Specialty)</v>
+        <v>Tier 3 Rx (Non-Preferred Brand)</v>
       </c>
       <c r="E10" t="str">
-        <v>Not covered</v>
+        <v>$75.00</v>
+      </c>
+      <c r="F10">
+        <v>75</v>
       </c>
       <c r="H10" t="str">
         <v>No</v>
@@ -837,16 +840,16 @@
         <v>OPTIMYL-1</v>
       </c>
       <c r="B11" t="str">
-        <v>OPTIMYL RBP 1500 7000</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11" t="str">
-        <v>Telemedicine (Physician + Behavioral Health)</v>
+        <v>Tier 4 Rx (Specialty)</v>
       </c>
       <c r="E11" t="str">
-        <v>Included</v>
+        <v>Not covered</v>
       </c>
       <c r="H11" t="str">
         <v>No</v>
@@ -857,22 +860,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>OPTIMYL-2</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B12" t="str">
-        <v>OPTIMYL RBP 2500 7000</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D12" t="str">
-        <v>Primary Care (Office)</v>
+        <v>Telemedicine (Physician + Behavioral Health)</v>
       </c>
       <c r="E12" t="str">
-        <v>$40.00</v>
-      </c>
-      <c r="F12">
-        <v>40</v>
+        <v>Included</v>
       </c>
       <c r="H12" t="str">
         <v>No</v>
@@ -886,19 +886,19 @@
         <v>OPTIMYL-2</v>
       </c>
       <c r="B13" t="str">
-        <v>OPTIMYL RBP 2500 7000</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="str">
-        <v>Specialist (Office)</v>
+        <v>Primary Care (Office)</v>
       </c>
       <c r="E13" t="str">
-        <v>$80.00</v>
+        <v>$40.00</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H13" t="str">
         <v>No</v>
@@ -912,19 +912,19 @@
         <v>OPTIMYL-2</v>
       </c>
       <c r="B14" t="str">
-        <v>OPTIMYL RBP 2500 7000</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="str">
-        <v>Urgent Care</v>
+        <v>Specialist (Office)</v>
       </c>
       <c r="E14" t="str">
-        <v>$100.00</v>
+        <v>$80.00</v>
       </c>
       <c r="F14">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H14" t="str">
         <v>No</v>
@@ -938,22 +938,22 @@
         <v>OPTIMYL-2</v>
       </c>
       <c r="B15" t="str">
-        <v>OPTIMYL RBP 2500 7000</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="str">
-        <v>Emergency Room</v>
+        <v>Urgent Care</v>
       </c>
       <c r="E15" t="str">
-        <v>Ded &amp; coins</v>
-      </c>
-      <c r="G15">
-        <v>0.2</v>
+        <v>$100.00</v>
+      </c>
+      <c r="F15">
+        <v>100</v>
       </c>
       <c r="H15" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I15">
         <v>2</v>
@@ -964,19 +964,19 @@
         <v>OPTIMYL-2</v>
       </c>
       <c r="B16" t="str">
-        <v>OPTIMYL RBP 2500 7000</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="str">
-        <v>Diagnostic Tests (X-Ray/Lab)</v>
+        <v>Emergency Room</v>
       </c>
       <c r="E16" t="str">
         <v>Ded &amp; coins</v>
       </c>
       <c r="G16">
-        <v>0.2</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H16" t="str">
         <v>Yes</v>
@@ -990,22 +990,22 @@
         <v>OPTIMYL-2</v>
       </c>
       <c r="B17" t="str">
-        <v>OPTIMYL RBP 2500 7000</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" t="str">
-        <v>Tier 1 Rx (Generic)</v>
+        <v>Diagnostic Tests (X-Ray/Lab)</v>
       </c>
       <c r="E17" t="str">
-        <v>$15.00</v>
-      </c>
-      <c r="F17">
-        <v>15</v>
+        <v>Ded &amp; coins</v>
+      </c>
+      <c r="G17">
+        <v>0.19999999999999996</v>
       </c>
       <c r="H17" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -1016,22 +1016,22 @@
         <v>OPTIMYL-2</v>
       </c>
       <c r="B18" t="str">
-        <v>OPTIMYL RBP 2500 7000</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18" t="str">
-        <v>Tier 2 Rx (Preferred Brand)</v>
+        <v>Inpatient Facility</v>
       </c>
       <c r="E18" t="str">
-        <v>$45.00</v>
-      </c>
-      <c r="F18">
-        <v>45</v>
+        <v>Ded &amp; coins</v>
+      </c>
+      <c r="G18">
+        <v>0.19999999999999996</v>
       </c>
       <c r="H18" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I18">
         <v>2</v>
@@ -1042,19 +1042,19 @@
         <v>OPTIMYL-2</v>
       </c>
       <c r="B19" t="str">
-        <v>OPTIMYL RBP 2500 7000</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" t="str">
-        <v>Tier 3 Rx (Non-Preferred Brand)</v>
+        <v>Tier 1 Rx (Generic)</v>
       </c>
       <c r="E19" t="str">
-        <v>$75.00</v>
+        <v>$15.00</v>
       </c>
       <c r="F19">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="H19" t="str">
         <v>No</v>
@@ -1068,16 +1068,19 @@
         <v>OPTIMYL-2</v>
       </c>
       <c r="B20" t="str">
-        <v>OPTIMYL RBP 2500 7000</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" t="str">
-        <v>Tier 4 Rx (Specialty)</v>
+        <v>Tier 2 Rx (Preferred Brand)</v>
       </c>
       <c r="E20" t="str">
-        <v>Not covered</v>
+        <v>$45.00</v>
+      </c>
+      <c r="F20">
+        <v>45</v>
       </c>
       <c r="H20" t="str">
         <v>No</v>
@@ -1091,16 +1094,19 @@
         <v>OPTIMYL-2</v>
       </c>
       <c r="B21" t="str">
-        <v>OPTIMYL RBP 2500 7000</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" t="str">
-        <v>Telemedicine (Physician + Behavioral Health)</v>
+        <v>Tier 3 Rx (Non-Preferred Brand)</v>
       </c>
       <c r="E21" t="str">
-        <v>Included</v>
+        <v>$75.00</v>
+      </c>
+      <c r="F21">
+        <v>75</v>
       </c>
       <c r="H21" t="str">
         <v>No</v>
@@ -1111,22 +1117,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>OPTIMYL-3</v>
+        <v>OPTIMYL-2</v>
       </c>
       <c r="B22" t="str">
-        <v>OPTIMYL RBP 3500 7000</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D22" t="str">
-        <v>Primary Care (Office)</v>
+        <v>Tier 4 Rx (Specialty)</v>
       </c>
       <c r="E22" t="str">
-        <v>$40.00</v>
-      </c>
-      <c r="F22">
-        <v>40</v>
+        <v>Not covered</v>
       </c>
       <c r="H22" t="str">
         <v>No</v>
@@ -1137,22 +1140,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>OPTIMYL-3</v>
+        <v>OPTIMYL-2</v>
       </c>
       <c r="B23" t="str">
-        <v>OPTIMYL RBP 3500 7000</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D23" t="str">
-        <v>Specialist (Office)</v>
+        <v>Telemedicine (Physician + Behavioral Health)</v>
       </c>
       <c r="E23" t="str">
-        <v>$80.00</v>
-      </c>
-      <c r="F23">
-        <v>80</v>
+        <v>Included</v>
       </c>
       <c r="H23" t="str">
         <v>No</v>
@@ -1166,19 +1166,19 @@
         <v>OPTIMYL-3</v>
       </c>
       <c r="B24" t="str">
-        <v>OPTIMYL RBP 3500 7000</v>
+        <v>OPTIMYL PLAN 3</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" t="str">
-        <v>Urgent Care</v>
+        <v>Primary Care (Office)</v>
       </c>
       <c r="E24" t="str">
-        <v>$100.00</v>
+        <v>$40.00</v>
       </c>
       <c r="F24">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H24" t="str">
         <v>No</v>
@@ -1192,22 +1192,22 @@
         <v>OPTIMYL-3</v>
       </c>
       <c r="B25" t="str">
-        <v>OPTIMYL RBP 3500 7000</v>
+        <v>OPTIMYL PLAN 3</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" t="str">
-        <v>Emergency Room</v>
+        <v>Specialist (Office)</v>
       </c>
       <c r="E25" t="str">
-        <v>Ded &amp; coins</v>
-      </c>
-      <c r="G25">
-        <v>0.3</v>
+        <v>$80.00</v>
+      </c>
+      <c r="F25">
+        <v>80</v>
       </c>
       <c r="H25" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I25">
         <v>2</v>
@@ -1218,22 +1218,22 @@
         <v>OPTIMYL-3</v>
       </c>
       <c r="B26" t="str">
-        <v>OPTIMYL RBP 3500 7000</v>
+        <v>OPTIMYL PLAN 3</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D26" t="str">
-        <v>Diagnostic Tests (X-Ray/Lab)</v>
+        <v>Urgent Care</v>
       </c>
       <c r="E26" t="str">
-        <v>Ded &amp; coins</v>
-      </c>
-      <c r="G26">
-        <v>0.3</v>
+        <v>$100.00</v>
+      </c>
+      <c r="F26">
+        <v>100</v>
       </c>
       <c r="H26" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I26">
         <v>2</v>
@@ -1244,22 +1244,22 @@
         <v>OPTIMYL-3</v>
       </c>
       <c r="B27" t="str">
-        <v>OPTIMYL RBP 3500 7000</v>
+        <v>OPTIMYL PLAN 3</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D27" t="str">
-        <v>Tier 1 Rx (Generic)</v>
+        <v>Emergency Room</v>
       </c>
       <c r="E27" t="str">
-        <v>$20.00</v>
-      </c>
-      <c r="F27">
-        <v>20</v>
+        <v>Ded &amp; coins</v>
+      </c>
+      <c r="G27">
+        <v>0.30000000000000004</v>
       </c>
       <c r="H27" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I27">
         <v>2</v>
@@ -1270,22 +1270,22 @@
         <v>OPTIMYL-3</v>
       </c>
       <c r="B28" t="str">
-        <v>OPTIMYL RBP 3500 7000</v>
+        <v>OPTIMYL PLAN 3</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D28" t="str">
-        <v>Tier 2 Rx (Preferred Brand)</v>
+        <v>Diagnostic Tests (X-Ray/Lab)</v>
       </c>
       <c r="E28" t="str">
-        <v>$50.00</v>
-      </c>
-      <c r="F28">
-        <v>50</v>
+        <v>Ded &amp; coins</v>
+      </c>
+      <c r="G28">
+        <v>0.30000000000000004</v>
       </c>
       <c r="H28" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I28">
         <v>2</v>
@@ -1296,22 +1296,22 @@
         <v>OPTIMYL-3</v>
       </c>
       <c r="B29" t="str">
-        <v>OPTIMYL RBP 3500 7000</v>
+        <v>OPTIMYL PLAN 3</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D29" t="str">
-        <v>Tier 3 Rx (Non-Preferred Brand)</v>
+        <v>Inpatient Facility</v>
       </c>
       <c r="E29" t="str">
-        <v>$100.00</v>
-      </c>
-      <c r="F29">
-        <v>100</v>
+        <v>Ded &amp; coins</v>
+      </c>
+      <c r="G29">
+        <v>0.30000000000000004</v>
       </c>
       <c r="H29" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I29">
         <v>2</v>
@@ -1322,16 +1322,19 @@
         <v>OPTIMYL-3</v>
       </c>
       <c r="B30" t="str">
-        <v>OPTIMYL RBP 3500 7000</v>
+        <v>OPTIMYL PLAN 3</v>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D30" t="str">
-        <v>Tier 4 Rx (Specialty)</v>
+        <v>Tier 1 Rx (Generic)</v>
       </c>
       <c r="E30" t="str">
-        <v>Not covered</v>
+        <v>$20.00</v>
+      </c>
+      <c r="F30">
+        <v>20</v>
       </c>
       <c r="H30" t="str">
         <v>No</v>
@@ -1345,16 +1348,19 @@
         <v>OPTIMYL-3</v>
       </c>
       <c r="B31" t="str">
-        <v>OPTIMYL RBP 3500 7000</v>
+        <v>OPTIMYL PLAN 3</v>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D31" t="str">
-        <v>Telemedicine (Physician + Behavioral Health)</v>
+        <v>Tier 2 Rx (Preferred Brand)</v>
       </c>
       <c r="E31" t="str">
-        <v>Included</v>
+        <v>$50.00</v>
+      </c>
+      <c r="F31">
+        <v>50</v>
       </c>
       <c r="H31" t="str">
         <v>No</v>
@@ -1365,22 +1371,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>OPTIMYL-4</v>
+        <v>OPTIMYL-3</v>
       </c>
       <c r="B32" t="str">
-        <v>OPTIMYL RBP 4500 9000</v>
+        <v>OPTIMYL PLAN 3</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D32" t="str">
-        <v>Primary Care (Office)</v>
+        <v>Tier 3 Rx (Non-Preferred Brand)</v>
       </c>
       <c r="E32" t="str">
-        <v>$40.00</v>
+        <v>$100.00</v>
       </c>
       <c r="F32">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="H32" t="str">
         <v>No</v>
@@ -1391,22 +1397,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>OPTIMYL-4</v>
+        <v>OPTIMYL-3</v>
       </c>
       <c r="B33" t="str">
-        <v>OPTIMYL RBP 4500 9000</v>
+        <v>OPTIMYL PLAN 3</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D33" t="str">
-        <v>Specialist (Office)</v>
+        <v>Tier 4 Rx (Specialty)</v>
       </c>
       <c r="E33" t="str">
-        <v>$80.00</v>
-      </c>
-      <c r="F33">
-        <v>80</v>
+        <v>Not covered</v>
       </c>
       <c r="H33" t="str">
         <v>No</v>
@@ -1417,22 +1420,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>OPTIMYL-4</v>
+        <v>OPTIMYL-3</v>
       </c>
       <c r="B34" t="str">
-        <v>OPTIMYL RBP 4500 9000</v>
+        <v>OPTIMYL PLAN 3</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D34" t="str">
-        <v>Urgent Care</v>
+        <v>Telemedicine (Physician + Behavioral Health)</v>
       </c>
       <c r="E34" t="str">
-        <v>$100.00</v>
-      </c>
-      <c r="F34">
-        <v>100</v>
+        <v>Included</v>
       </c>
       <c r="H34" t="str">
         <v>No</v>
@@ -1446,22 +1446,22 @@
         <v>OPTIMYL-4</v>
       </c>
       <c r="B35" t="str">
-        <v>OPTIMYL RBP 4500 9000</v>
+        <v>OPTIMYL PLAN 4</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D35" t="str">
-        <v>Emergency Room</v>
+        <v>Primary Care (Office)</v>
       </c>
       <c r="E35" t="str">
-        <v>Ded &amp; coins</v>
-      </c>
-      <c r="G35">
-        <v>0.5</v>
+        <v>$40.00</v>
+      </c>
+      <c r="F35">
+        <v>40</v>
       </c>
       <c r="H35" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I35">
         <v>2</v>
@@ -1472,22 +1472,22 @@
         <v>OPTIMYL-4</v>
       </c>
       <c r="B36" t="str">
-        <v>OPTIMYL RBP 4500 9000</v>
+        <v>OPTIMYL PLAN 4</v>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D36" t="str">
-        <v>Diagnostic Tests (X-Ray/Lab)</v>
+        <v>Specialist (Office)</v>
       </c>
       <c r="E36" t="str">
-        <v>Ded &amp; coins</v>
-      </c>
-      <c r="G36">
-        <v>0.5</v>
+        <v>$80.00</v>
+      </c>
+      <c r="F36">
+        <v>80</v>
       </c>
       <c r="H36" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I36">
         <v>2</v>
@@ -1498,19 +1498,19 @@
         <v>OPTIMYL-4</v>
       </c>
       <c r="B37" t="str">
-        <v>OPTIMYL RBP 4500 9000</v>
+        <v>OPTIMYL PLAN 4</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D37" t="str">
-        <v>Tier 1 Rx (Generic)</v>
+        <v>Urgent Care</v>
       </c>
       <c r="E37" t="str">
-        <v>$20.00</v>
+        <v>$100.00</v>
       </c>
       <c r="F37">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="H37" t="str">
         <v>No</v>
@@ -1524,22 +1524,22 @@
         <v>OPTIMYL-4</v>
       </c>
       <c r="B38" t="str">
-        <v>OPTIMYL RBP 4500 9000</v>
+        <v>OPTIMYL PLAN 4</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D38" t="str">
-        <v>Tier 2 Rx (Preferred Brand)</v>
+        <v>Emergency Room</v>
       </c>
       <c r="E38" t="str">
-        <v>$50.00</v>
-      </c>
-      <c r="F38">
-        <v>50</v>
+        <v>Ded &amp; coins</v>
+      </c>
+      <c r="G38">
+        <v>0.5</v>
       </c>
       <c r="H38" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I38">
         <v>2</v>
@@ -1550,22 +1550,22 @@
         <v>OPTIMYL-4</v>
       </c>
       <c r="B39" t="str">
-        <v>OPTIMYL RBP 4500 9000</v>
+        <v>OPTIMYL PLAN 4</v>
       </c>
       <c r="C39">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D39" t="str">
-        <v>Tier 3 Rx (Non-Preferred Brand)</v>
+        <v>Diagnostic Tests (X-Ray/Lab)</v>
       </c>
       <c r="E39" t="str">
-        <v>$100.00</v>
-      </c>
-      <c r="F39">
-        <v>100</v>
+        <v>Ded &amp; coins</v>
+      </c>
+      <c r="G39">
+        <v>0.5</v>
       </c>
       <c r="H39" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I39">
         <v>2</v>
@@ -1576,19 +1576,22 @@
         <v>OPTIMYL-4</v>
       </c>
       <c r="B40" t="str">
-        <v>OPTIMYL RBP 4500 9000</v>
+        <v>OPTIMYL PLAN 4</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D40" t="str">
-        <v>Tier 4 Rx (Specialty)</v>
+        <v>Inpatient Facility</v>
       </c>
       <c r="E40" t="str">
-        <v>Not covered</v>
+        <v>Ded &amp; coins</v>
+      </c>
+      <c r="G40">
+        <v>0.5</v>
       </c>
       <c r="H40" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I40">
         <v>2</v>
@@ -1599,34 +1602,135 @@
         <v>OPTIMYL-4</v>
       </c>
       <c r="B41" t="str">
-        <v>OPTIMYL RBP 4500 9000</v>
+        <v>OPTIMYL PLAN 4</v>
       </c>
       <c r="C41">
+        <v>7</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Tier 1 Rx (Generic)</v>
+      </c>
+      <c r="E41" t="str">
+        <v>$20.00</v>
+      </c>
+      <c r="F41">
+        <v>20</v>
+      </c>
+      <c r="H41" t="str">
+        <v>No</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B42" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C42">
+        <v>8</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Tier 2 Rx (Preferred Brand)</v>
+      </c>
+      <c r="E42" t="str">
+        <v>$50.00</v>
+      </c>
+      <c r="F42">
+        <v>50</v>
+      </c>
+      <c r="H42" t="str">
+        <v>No</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B43" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C43">
+        <v>9</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Tier 3 Rx (Non-Preferred Brand)</v>
+      </c>
+      <c r="E43" t="str">
+        <v>$100.00</v>
+      </c>
+      <c r="F43">
+        <v>100</v>
+      </c>
+      <c r="H43" t="str">
+        <v>No</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B44" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C44">
         <v>10</v>
       </c>
-      <c r="D41" t="str">
+      <c r="D44" t="str">
+        <v>Tier 4 Rx (Specialty)</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Not covered</v>
+      </c>
+      <c r="H44" t="str">
+        <v>No</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B45" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C45">
+        <v>11</v>
+      </c>
+      <c r="D45" t="str">
         <v>Telemedicine (Physician + Behavioral Health)</v>
       </c>
-      <c r="E41" t="str">
+      <c r="E45" t="str">
         <v>Included</v>
       </c>
-      <c r="H41" t="str">
-        <v>No</v>
-      </c>
-      <c r="I41">
+      <c r="H45" t="str">
+        <v>No</v>
+      </c>
+      <c r="I45">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I45"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1649,7 +1753,7 @@
         <v>Program</v>
       </c>
       <c r="B3" t="str">
-        <v>Optimyl Benefits Self-Funded Program: reference-based pricing (RBP), network "RBP Full". Stop Loss is underwritten by The North River Insurance Company or Gerber Life Insurance Company.</v>
+        <v>Optimyl Benefits Self-Funded Program: reference-based pricing (RBP), network "RBP Full". Stop Loss is underwritten by The North River Insurance Company or Gerber Life Insurance Company. Pharmacy benefit manager: CVS (closed formulary).</v>
       </c>
     </row>
     <row r="4">
@@ -1665,7 +1769,7 @@
         <v>Plan name / code</v>
       </c>
       <c r="B5" t="str">
-        <v>plan_name_code is a Kennion-assigned label ("OPTIMYL RBP &lt;individual deductible&gt; &lt;individual OOP max&gt;") - the source proposal only numbers plans 1-4, it prints no carrier plan code.</v>
+        <v>plan_name_code is "OPTIMYL PLAN &lt;n&gt;", from the proposal's own "Plan Number" row (1-4) - the only number or code Optimyl prints for a plan. server/ai.js tells the reader to set plan_code the same way, so every Optimyl proposal's 4 plans match this catalogue by that code alone.</v>
       </c>
     </row>
     <row r="6">
@@ -1673,7 +1777,7 @@
         <v>Reuse across groups</v>
       </c>
       <c r="B6" t="str">
-        <v>Optimyl quotes these same 4 designs to every group; only composite rates, stop-loss premium and admin fees differ per group's census and are read from each group's own uploaded proposal, not from this catalogue.</v>
+        <v>Optimyl quotes these same 4 designs, numbered 1-4 in this same order, to every group; only composite rates, stop-loss premium and admin fees differ per group's census and are read from each group's own uploaded proposal, not from this catalogue.</v>
       </c>
     </row>
     <row r="7">
@@ -1686,31 +1790,39 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Numeric values</v>
+        <v>Inpatient Facility</v>
       </c>
       <c r="B8" t="str">
-        <v>Dollar amounts are numeric USD. Percentage fields are decimals: 0.20 means 20%. Blank dollar/percentage fields mean that unit is not used for the benefit.</v>
+        <v>Not printed as its own line on the proposal's summary grid; given the same deductible-then-coinsurance cost share the grid states explicitly for Emergency Room and X-ray/Lab, since that is the RBP program's default cost share for a covered service with no separate copay.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Out-of-network</v>
+        <v>Numeric values</v>
       </c>
       <c r="B9" t="str">
-        <v>The proposal gives no separate out-of-network figures (RBP has no traditional network split), so the oon_* columns are blank.</v>
+        <v>Dollar amounts are numeric USD. Percentage fields are decimals: 0.20 means 20%. Blank dollar/percentage fields mean that unit is not used for the benefit.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>Out-of-network</v>
+      </c>
+      <c r="B10" t="str">
+        <v>The proposal gives no separate out-of-network figures (RBP has no traditional network split), so the oon_* columns are blank.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>Specialty Rx</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B11" t="str">
         <v>Specialty drugs are not covered under any of the 4 plans per the proposal's Terms page.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/server/data/plan-docs/OptimylHealthStandardPlanBenefits.xlsx
+++ b/server/data/plan-docs/OptimylHealthStandardPlanBenefits.xlsx
@@ -570,7 +570,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I137"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -615,7 +615,7 @@
         <v>Primary Care (Office)</v>
       </c>
       <c r="E2" t="str">
-        <v>$30.00</v>
+        <v>$30.00 copay/office visit (20% coinsurance for other outpatient services)</v>
       </c>
       <c r="F2">
         <v>30</v>
@@ -664,13 +664,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="str">
-        <v>Urgent Care</v>
+        <v>Preventive Care / Screening / Immunization</v>
       </c>
       <c r="E4" t="str">
-        <v>$75.00</v>
+        <v>No charge</v>
       </c>
       <c r="F4">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H4" t="str">
         <v>No</v>
@@ -690,10 +690,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="str">
-        <v>Emergency Room</v>
+        <v>Diagnostic Tests (X-Ray/Lab)</v>
       </c>
       <c r="E5" t="str">
-        <v>Ded &amp; coins</v>
+        <v>20%</v>
       </c>
       <c r="G5">
         <v>0.19999999999999996</v>
@@ -716,10 +716,10 @@
         <v>5</v>
       </c>
       <c r="D6" t="str">
-        <v>Diagnostic Tests (X-Ray/Lab)</v>
+        <v>Imaging (CT/PET/MRI)</v>
       </c>
       <c r="E6" t="str">
-        <v>Ded &amp; coins</v>
+        <v>20% coinsurance; preauthorization required</v>
       </c>
       <c r="G6">
         <v>0.19999999999999996</v>
@@ -742,16 +742,16 @@
         <v>6</v>
       </c>
       <c r="D7" t="str">
-        <v>Inpatient Facility</v>
+        <v>Tier 1 Rx (Generic, Retail)</v>
       </c>
       <c r="E7" t="str">
-        <v>Ded &amp; coins</v>
-      </c>
-      <c r="G7">
-        <v>0.19999999999999996</v>
+        <v>$15.00</v>
+      </c>
+      <c r="F7">
+        <v>15</v>
       </c>
       <c r="H7" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -768,13 +768,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="str">
-        <v>Tier 1 Rx (Generic)</v>
+        <v>Tier 1 Rx (Generic, Mail Order)</v>
       </c>
       <c r="E8" t="str">
-        <v>$15.00</v>
+        <v>$37.50</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>37.5</v>
       </c>
       <c r="H8" t="str">
         <v>No</v>
@@ -794,7 +794,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="str">
-        <v>Tier 2 Rx (Preferred Brand)</v>
+        <v>Tier 2 Rx (Preferred Brand, Retail)</v>
       </c>
       <c r="E9" t="str">
         <v>$45.00</v>
@@ -820,13 +820,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="str">
-        <v>Tier 3 Rx (Non-Preferred Brand)</v>
+        <v>Tier 2 Rx (Preferred Brand, Mail Order)</v>
       </c>
       <c r="E10" t="str">
-        <v>$75.00</v>
+        <v>$112.50</v>
       </c>
       <c r="F10">
-        <v>75</v>
+        <v>112.5</v>
       </c>
       <c r="H10" t="str">
         <v>No</v>
@@ -846,10 +846,13 @@
         <v>10</v>
       </c>
       <c r="D11" t="str">
-        <v>Tier 4 Rx (Specialty)</v>
+        <v>Tier 3 Rx (Non-Preferred Brand, Retail)</v>
       </c>
       <c r="E11" t="str">
-        <v>Not covered</v>
+        <v>$75.00</v>
+      </c>
+      <c r="F11">
+        <v>75</v>
       </c>
       <c r="H11" t="str">
         <v>No</v>
@@ -869,10 +872,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="str">
-        <v>Telemedicine (Physician + Behavioral Health)</v>
+        <v>Tier 3 Rx (Non-Preferred Brand, Mail Order)</v>
       </c>
       <c r="E12" t="str">
-        <v>Included</v>
+        <v>$187.50</v>
+      </c>
+      <c r="F12">
+        <v>187.5</v>
       </c>
       <c r="H12" t="str">
         <v>No</v>
@@ -883,22 +889,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>OPTIMYL-2</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B13" t="str">
-        <v>OPTIMYL PLAN 2</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D13" t="str">
-        <v>Primary Care (Office)</v>
+        <v>Tier 4 Rx (Specialty)</v>
       </c>
       <c r="E13" t="str">
-        <v>$40.00</v>
-      </c>
-      <c r="F13">
-        <v>40</v>
+        <v>Not covered</v>
       </c>
       <c r="H13" t="str">
         <v>No</v>
@@ -909,25 +912,25 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>OPTIMYL-2</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B14" t="str">
-        <v>OPTIMYL PLAN 2</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D14" t="str">
-        <v>Specialist (Office)</v>
+        <v>Outpatient Surgery - Facility Fee</v>
       </c>
       <c r="E14" t="str">
-        <v>$80.00</v>
-      </c>
-      <c r="F14">
-        <v>80</v>
+        <v>20% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G14">
+        <v>0.19999999999999996</v>
       </c>
       <c r="H14" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -935,25 +938,25 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>OPTIMYL-2</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B15" t="str">
-        <v>OPTIMYL PLAN 2</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D15" t="str">
-        <v>Urgent Care</v>
+        <v>Outpatient Surgery - Physician/Surgeon Fees</v>
       </c>
       <c r="E15" t="str">
-        <v>$100.00</v>
-      </c>
-      <c r="F15">
-        <v>100</v>
+        <v>20% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G15">
+        <v>0.19999999999999996</v>
       </c>
       <c r="H15" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I15">
         <v>2</v>
@@ -961,19 +964,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>OPTIMYL-2</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B16" t="str">
-        <v>OPTIMYL PLAN 2</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D16" t="str">
         <v>Emergency Room</v>
       </c>
       <c r="E16" t="str">
-        <v>Ded &amp; coins</v>
+        <v>20% coinsurance; non-emergency use reduces covered charges by 25%</v>
       </c>
       <c r="G16">
         <v>0.19999999999999996</v>
@@ -987,19 +990,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>OPTIMYL-2</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B17" t="str">
-        <v>OPTIMYL PLAN 2</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D17" t="str">
-        <v>Diagnostic Tests (X-Ray/Lab)</v>
+        <v>Emergency Medical Transportation</v>
       </c>
       <c r="E17" t="str">
-        <v>Ded &amp; coins</v>
+        <v>20%</v>
       </c>
       <c r="G17">
         <v>0.19999999999999996</v>
@@ -1013,25 +1016,25 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>OPTIMYL-2</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B18" t="str">
-        <v>OPTIMYL PLAN 2</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D18" t="str">
-        <v>Inpatient Facility</v>
+        <v>Urgent Care</v>
       </c>
       <c r="E18" t="str">
-        <v>Ded &amp; coins</v>
-      </c>
-      <c r="G18">
-        <v>0.19999999999999996</v>
+        <v>$75.00</v>
+      </c>
+      <c r="F18">
+        <v>75</v>
       </c>
       <c r="H18" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I18">
         <v>2</v>
@@ -1039,25 +1042,25 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>OPTIMYL-2</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B19" t="str">
-        <v>OPTIMYL PLAN 2</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D19" t="str">
-        <v>Tier 1 Rx (Generic)</v>
+        <v>Inpatient Facility</v>
       </c>
       <c r="E19" t="str">
-        <v>$15.00</v>
-      </c>
-      <c r="F19">
-        <v>15</v>
+        <v>20% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G19">
+        <v>0.19999999999999996</v>
       </c>
       <c r="H19" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I19">
         <v>2</v>
@@ -1065,25 +1068,25 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>OPTIMYL-2</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B20" t="str">
-        <v>OPTIMYL PLAN 2</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D20" t="str">
-        <v>Tier 2 Rx (Preferred Brand)</v>
+        <v>Hospital - Physician/Surgeon Fees</v>
       </c>
       <c r="E20" t="str">
-        <v>$45.00</v>
-      </c>
-      <c r="F20">
-        <v>45</v>
+        <v>20% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G20">
+        <v>0.19999999999999996</v>
       </c>
       <c r="H20" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -1091,25 +1094,25 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>OPTIMYL-2</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B21" t="str">
-        <v>OPTIMYL PLAN 2</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D21" t="str">
-        <v>Tier 3 Rx (Non-Preferred Brand)</v>
+        <v>Mental/Behavioral Health - Outpatient</v>
       </c>
       <c r="E21" t="str">
-        <v>$75.00</v>
-      </c>
-      <c r="F21">
-        <v>75</v>
+        <v>50% coinsurance; preauthorization required; 30 visit/year limit</v>
+      </c>
+      <c r="G21">
+        <v>0.5</v>
       </c>
       <c r="H21" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I21">
         <v>2</v>
@@ -1117,22 +1120,25 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>OPTIMYL-2</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B22" t="str">
-        <v>OPTIMYL PLAN 2</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D22" t="str">
-        <v>Tier 4 Rx (Specialty)</v>
+        <v>Mental/Behavioral Health - Inpatient</v>
       </c>
       <c r="E22" t="str">
-        <v>Not covered</v>
+        <v>50% coinsurance; preauthorization required; 30 day/year limit</v>
+      </c>
+      <c r="G22">
+        <v>0.5</v>
       </c>
       <c r="H22" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I22">
         <v>2</v>
@@ -1140,19 +1146,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>OPTIMYL-2</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B23" t="str">
-        <v>OPTIMYL PLAN 2</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D23" t="str">
-        <v>Telemedicine (Physician + Behavioral Health)</v>
+        <v>Maternity - Office Visits</v>
       </c>
       <c r="E23" t="str">
-        <v>Included</v>
+        <v>$30.00 copay/office visit (20% coinsurance for other outpatient services); no cost sharing for preventive services</v>
+      </c>
+      <c r="F23">
+        <v>30</v>
       </c>
       <c r="H23" t="str">
         <v>No</v>
@@ -1163,25 +1172,25 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>OPTIMYL-3</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B24" t="str">
-        <v>OPTIMYL PLAN 3</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D24" t="str">
-        <v>Primary Care (Office)</v>
+        <v>Maternity - Delivery, Professional</v>
       </c>
       <c r="E24" t="str">
-        <v>$40.00</v>
-      </c>
-      <c r="F24">
-        <v>40</v>
+        <v>20% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G24">
+        <v>0.19999999999999996</v>
       </c>
       <c r="H24" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I24">
         <v>2</v>
@@ -1189,25 +1198,25 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>OPTIMYL-3</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B25" t="str">
-        <v>OPTIMYL PLAN 3</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D25" t="str">
-        <v>Specialist (Office)</v>
+        <v>Maternity - Delivery, Facility</v>
       </c>
       <c r="E25" t="str">
-        <v>$80.00</v>
-      </c>
-      <c r="F25">
-        <v>80</v>
+        <v>20% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G25">
+        <v>0.19999999999999996</v>
       </c>
       <c r="H25" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I25">
         <v>2</v>
@@ -1215,25 +1224,25 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>OPTIMYL-3</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B26" t="str">
-        <v>OPTIMYL PLAN 3</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D26" t="str">
-        <v>Urgent Care</v>
+        <v>Home Health Care</v>
       </c>
       <c r="E26" t="str">
-        <v>$100.00</v>
-      </c>
-      <c r="F26">
-        <v>100</v>
+        <v>20% coinsurance; preauthorization required; 45 visit/year limit</v>
+      </c>
+      <c r="G26">
+        <v>0.19999999999999996</v>
       </c>
       <c r="H26" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I26">
         <v>2</v>
@@ -1241,22 +1250,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>OPTIMYL-3</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B27" t="str">
-        <v>OPTIMYL PLAN 3</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D27" t="str">
-        <v>Emergency Room</v>
+        <v>Rehabilitation Services</v>
       </c>
       <c r="E27" t="str">
-        <v>Ded &amp; coins</v>
+        <v>20% coinsurance; preauthorization required (inpatient); inpatient 30 day/year limit combined with skilled nursing; outpatient 30 visit/year limit</v>
       </c>
       <c r="G27">
-        <v>0.30000000000000004</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H27" t="str">
         <v>Yes</v>
@@ -1267,22 +1276,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>OPTIMYL-3</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B28" t="str">
-        <v>OPTIMYL PLAN 3</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D28" t="str">
-        <v>Diagnostic Tests (X-Ray/Lab)</v>
+        <v>Habilitation Services</v>
       </c>
       <c r="E28" t="str">
-        <v>Ded &amp; coins</v>
+        <v>20% coinsurance; same combined limits as rehabilitation services</v>
       </c>
       <c r="G28">
-        <v>0.30000000000000004</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H28" t="str">
         <v>Yes</v>
@@ -1293,22 +1302,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>OPTIMYL-3</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B29" t="str">
-        <v>OPTIMYL PLAN 3</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D29" t="str">
-        <v>Inpatient Facility</v>
+        <v>Skilled Nursing Care</v>
       </c>
       <c r="E29" t="str">
-        <v>Ded &amp; coins</v>
+        <v>20% coinsurance; preauthorization required; 30 day/year limit combined with inpatient rehabilitation</v>
       </c>
       <c r="G29">
-        <v>0.30000000000000004</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H29" t="str">
         <v>Yes</v>
@@ -1319,25 +1328,25 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>OPTIMYL-3</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B30" t="str">
-        <v>OPTIMYL PLAN 3</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D30" t="str">
-        <v>Tier 1 Rx (Generic)</v>
+        <v>Durable Medical Equipment</v>
       </c>
       <c r="E30" t="str">
-        <v>$20.00</v>
-      </c>
-      <c r="F30">
-        <v>20</v>
+        <v>20% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G30">
+        <v>0.19999999999999996</v>
       </c>
       <c r="H30" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I30">
         <v>2</v>
@@ -1345,25 +1354,25 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>OPTIMYL-3</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B31" t="str">
-        <v>OPTIMYL PLAN 3</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D31" t="str">
-        <v>Tier 2 Rx (Preferred Brand)</v>
+        <v>Hospice Services</v>
       </c>
       <c r="E31" t="str">
-        <v>$50.00</v>
-      </c>
-      <c r="F31">
-        <v>50</v>
+        <v>20% coinsurance; preauthorization required; 180 day/year limit</v>
+      </c>
+      <c r="G31">
+        <v>0.19999999999999996</v>
       </c>
       <c r="H31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="I31">
         <v>2</v>
@@ -1371,22 +1380,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>OPTIMYL-3</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B32" t="str">
-        <v>OPTIMYL PLAN 3</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D32" t="str">
-        <v>Tier 3 Rx (Non-Preferred Brand)</v>
+        <v>Children's Eye Exam</v>
       </c>
       <c r="E32" t="str">
-        <v>$100.00</v>
-      </c>
-      <c r="F32">
-        <v>100</v>
+        <v>Not covered</v>
       </c>
       <c r="H32" t="str">
         <v>No</v>
@@ -1397,16 +1403,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>OPTIMYL-3</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B33" t="str">
-        <v>OPTIMYL PLAN 3</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D33" t="str">
-        <v>Tier 4 Rx (Specialty)</v>
+        <v>Children's Glasses</v>
       </c>
       <c r="E33" t="str">
         <v>Not covered</v>
@@ -1420,19 +1426,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>OPTIMYL-3</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B34" t="str">
-        <v>OPTIMYL PLAN 3</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C34">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D34" t="str">
-        <v>Telemedicine (Physician + Behavioral Health)</v>
+        <v>Children's Dental Check-Up</v>
       </c>
       <c r="E34" t="str">
-        <v>Included</v>
+        <v>Not covered</v>
       </c>
       <c r="H34" t="str">
         <v>No</v>
@@ -1443,22 +1449,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>OPTIMYL-4</v>
+        <v>OPTIMYL-1</v>
       </c>
       <c r="B35" t="str">
-        <v>OPTIMYL PLAN 4</v>
+        <v>OPTIMYL PLAN 1</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D35" t="str">
-        <v>Primary Care (Office)</v>
+        <v>Telemedicine (Physician + Behavioral Health)</v>
       </c>
       <c r="E35" t="str">
-        <v>$40.00</v>
-      </c>
-      <c r="F35">
-        <v>40</v>
+        <v>Included, per the carrier's proposal summary</v>
       </c>
       <c r="H35" t="str">
         <v>No</v>
@@ -1469,22 +1472,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>OPTIMYL-4</v>
+        <v>OPTIMYL-2</v>
       </c>
       <c r="B36" t="str">
-        <v>OPTIMYL PLAN 4</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="str">
-        <v>Specialist (Office)</v>
+        <v>Primary Care (Office)</v>
       </c>
       <c r="E36" t="str">
-        <v>$80.00</v>
+        <v>$40.00 copay/office visit (20% coinsurance for other outpatient services)</v>
       </c>
       <c r="F36">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H36" t="str">
         <v>No</v>
@@ -1495,22 +1498,22 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>OPTIMYL-4</v>
+        <v>OPTIMYL-2</v>
       </c>
       <c r="B37" t="str">
-        <v>OPTIMYL PLAN 4</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" t="str">
-        <v>Urgent Care</v>
+        <v>Specialist (Office)</v>
       </c>
       <c r="E37" t="str">
-        <v>$100.00</v>
+        <v>$80.00</v>
       </c>
       <c r="F37">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H37" t="str">
         <v>No</v>
@@ -1521,25 +1524,25 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>OPTIMYL-4</v>
+        <v>OPTIMYL-2</v>
       </c>
       <c r="B38" t="str">
-        <v>OPTIMYL PLAN 4</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38" t="str">
-        <v>Emergency Room</v>
+        <v>Preventive Care / Screening / Immunization</v>
       </c>
       <c r="E38" t="str">
-        <v>Ded &amp; coins</v>
-      </c>
-      <c r="G38">
-        <v>0.5</v>
+        <v>No charge</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
       </c>
       <c r="H38" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="I38">
         <v>2</v>
@@ -1547,22 +1550,22 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>OPTIMYL-4</v>
+        <v>OPTIMYL-2</v>
       </c>
       <c r="B39" t="str">
-        <v>OPTIMYL PLAN 4</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" t="str">
         <v>Diagnostic Tests (X-Ray/Lab)</v>
       </c>
       <c r="E39" t="str">
-        <v>Ded &amp; coins</v>
+        <v>20%</v>
       </c>
       <c r="G39">
-        <v>0.5</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H39" t="str">
         <v>Yes</v>
@@ -1573,22 +1576,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>OPTIMYL-4</v>
+        <v>OPTIMYL-2</v>
       </c>
       <c r="B40" t="str">
-        <v>OPTIMYL PLAN 4</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D40" t="str">
-        <v>Inpatient Facility</v>
+        <v>Imaging (CT/PET/MRI)</v>
       </c>
       <c r="E40" t="str">
-        <v>Ded &amp; coins</v>
+        <v>20% coinsurance; preauthorization required</v>
       </c>
       <c r="G40">
-        <v>0.5</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H40" t="str">
         <v>Yes</v>
@@ -1599,22 +1602,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>OPTIMYL-4</v>
+        <v>OPTIMYL-2</v>
       </c>
       <c r="B41" t="str">
-        <v>OPTIMYL PLAN 4</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D41" t="str">
-        <v>Tier 1 Rx (Generic)</v>
+        <v>Tier 1 Rx (Generic, Retail)</v>
       </c>
       <c r="E41" t="str">
-        <v>$20.00</v>
+        <v>$15.00</v>
       </c>
       <c r="F41">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H41" t="str">
         <v>No</v>
@@ -1625,22 +1628,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>OPTIMYL-4</v>
+        <v>OPTIMYL-2</v>
       </c>
       <c r="B42" t="str">
-        <v>OPTIMYL PLAN 4</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D42" t="str">
-        <v>Tier 2 Rx (Preferred Brand)</v>
+        <v>Tier 1 Rx (Generic, Mail Order)</v>
       </c>
       <c r="E42" t="str">
-        <v>$50.00</v>
+        <v>$37.50</v>
       </c>
       <c r="F42">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="H42" t="str">
         <v>No</v>
@@ -1651,22 +1654,22 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>OPTIMYL-4</v>
+        <v>OPTIMYL-2</v>
       </c>
       <c r="B43" t="str">
-        <v>OPTIMYL PLAN 4</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43" t="str">
-        <v>Tier 3 Rx (Non-Preferred Brand)</v>
+        <v>Tier 2 Rx (Preferred Brand, Retail)</v>
       </c>
       <c r="E43" t="str">
-        <v>$100.00</v>
+        <v>$45.00</v>
       </c>
       <c r="F43">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="H43" t="str">
         <v>No</v>
@@ -1677,19 +1680,22 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>OPTIMYL-4</v>
+        <v>OPTIMYL-2</v>
       </c>
       <c r="B44" t="str">
-        <v>OPTIMYL PLAN 4</v>
+        <v>OPTIMYL PLAN 2</v>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D44" t="str">
-        <v>Tier 4 Rx (Specialty)</v>
+        <v>Tier 2 Rx (Preferred Brand, Mail Order)</v>
       </c>
       <c r="E44" t="str">
-        <v>Not covered</v>
+        <v>$112.50</v>
+      </c>
+      <c r="F44">
+        <v>112.5</v>
       </c>
       <c r="H44" t="str">
         <v>No</v>
@@ -1700,30 +1706,2380 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B45" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C45">
+        <v>10</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Tier 3 Rx (Non-Preferred Brand, Retail)</v>
+      </c>
+      <c r="E45" t="str">
+        <v>$75.00</v>
+      </c>
+      <c r="F45">
+        <v>75</v>
+      </c>
+      <c r="H45" t="str">
+        <v>No</v>
+      </c>
+      <c r="I45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B46" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C46">
+        <v>11</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Tier 3 Rx (Non-Preferred Brand, Mail Order)</v>
+      </c>
+      <c r="E46" t="str">
+        <v>$187.50</v>
+      </c>
+      <c r="F46">
+        <v>187.5</v>
+      </c>
+      <c r="H46" t="str">
+        <v>No</v>
+      </c>
+      <c r="I46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B47" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C47">
+        <v>12</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Tier 4 Rx (Specialty)</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Not covered</v>
+      </c>
+      <c r="H47" t="str">
+        <v>No</v>
+      </c>
+      <c r="I47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B48" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C48">
+        <v>13</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Outpatient Surgery - Facility Fee</v>
+      </c>
+      <c r="E48" t="str">
+        <v>20% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G48">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B49" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C49">
+        <v>14</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Outpatient Surgery - Physician/Surgeon Fees</v>
+      </c>
+      <c r="E49" t="str">
+        <v>20% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G49">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B50" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C50">
+        <v>15</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Emergency Room</v>
+      </c>
+      <c r="E50" t="str">
+        <v>20% coinsurance; non-emergency use reduces covered charges by 25%</v>
+      </c>
+      <c r="G50">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B51" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C51">
+        <v>16</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Emergency Medical Transportation</v>
+      </c>
+      <c r="E51" t="str">
+        <v>20%</v>
+      </c>
+      <c r="G51">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B52" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C52">
+        <v>17</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Urgent Care</v>
+      </c>
+      <c r="E52" t="str">
+        <v>$100.00</v>
+      </c>
+      <c r="F52">
+        <v>100</v>
+      </c>
+      <c r="H52" t="str">
+        <v>No</v>
+      </c>
+      <c r="I52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B53" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C53">
+        <v>18</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Inpatient Facility</v>
+      </c>
+      <c r="E53" t="str">
+        <v>20% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G53">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B54" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C54">
+        <v>19</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Hospital - Physician/Surgeon Fees</v>
+      </c>
+      <c r="E54" t="str">
+        <v>20% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G54">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B55" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C55">
+        <v>20</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Mental/Behavioral Health - Outpatient</v>
+      </c>
+      <c r="E55" t="str">
+        <v>50% coinsurance; preauthorization required; 30 visit/year limit</v>
+      </c>
+      <c r="G55">
+        <v>0.5</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B56" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C56">
+        <v>21</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Mental/Behavioral Health - Inpatient</v>
+      </c>
+      <c r="E56" t="str">
+        <v>50% coinsurance; preauthorization required; 30 day/year limit</v>
+      </c>
+      <c r="G56">
+        <v>0.5</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B57" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C57">
+        <v>22</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Maternity - Office Visits</v>
+      </c>
+      <c r="E57" t="str">
+        <v>$40.00 copay/office visit (20% coinsurance for other outpatient services); no cost sharing for preventive services</v>
+      </c>
+      <c r="F57">
+        <v>40</v>
+      </c>
+      <c r="H57" t="str">
+        <v>No</v>
+      </c>
+      <c r="I57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B58" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C58">
+        <v>23</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Maternity - Delivery, Professional</v>
+      </c>
+      <c r="E58" t="str">
+        <v>20% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G58">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H58" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B59" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C59">
+        <v>24</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Maternity - Delivery, Facility</v>
+      </c>
+      <c r="E59" t="str">
+        <v>20% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G59">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H59" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B60" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C60">
+        <v>25</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Home Health Care</v>
+      </c>
+      <c r="E60" t="str">
+        <v>20% coinsurance; preauthorization required; 45 visit/year limit</v>
+      </c>
+      <c r="G60">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H60" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B61" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C61">
+        <v>26</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Rehabilitation Services</v>
+      </c>
+      <c r="E61" t="str">
+        <v>20% coinsurance; preauthorization required (inpatient); inpatient 30 day/year limit combined with skilled nursing; outpatient 30 visit/year limit</v>
+      </c>
+      <c r="G61">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B62" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C62">
+        <v>27</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Habilitation Services</v>
+      </c>
+      <c r="E62" t="str">
+        <v>20% coinsurance; same combined limits as rehabilitation services</v>
+      </c>
+      <c r="G62">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H62" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B63" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C63">
+        <v>28</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Skilled Nursing Care</v>
+      </c>
+      <c r="E63" t="str">
+        <v>20% coinsurance; preauthorization required; 30 day/year limit combined with inpatient rehabilitation</v>
+      </c>
+      <c r="G63">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B64" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C64">
+        <v>29</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Durable Medical Equipment</v>
+      </c>
+      <c r="E64" t="str">
+        <v>20% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G64">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H64" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B65" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C65">
+        <v>30</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Hospice Services</v>
+      </c>
+      <c r="E65" t="str">
+        <v>20% coinsurance; preauthorization required; 180 day/year limit</v>
+      </c>
+      <c r="G65">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B66" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C66">
+        <v>31</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Children's Eye Exam</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Not covered</v>
+      </c>
+      <c r="H66" t="str">
+        <v>No</v>
+      </c>
+      <c r="I66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B67" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C67">
+        <v>32</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Children's Glasses</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Not covered</v>
+      </c>
+      <c r="H67" t="str">
+        <v>No</v>
+      </c>
+      <c r="I67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B68" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C68">
+        <v>33</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Children's Dental Check-Up</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Not covered</v>
+      </c>
+      <c r="H68" t="str">
+        <v>No</v>
+      </c>
+      <c r="I68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>OPTIMYL-2</v>
+      </c>
+      <c r="B69" t="str">
+        <v>OPTIMYL PLAN 2</v>
+      </c>
+      <c r="C69">
+        <v>34</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Telemedicine (Physician + Behavioral Health)</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Included, per the carrier's proposal summary</v>
+      </c>
+      <c r="H69" t="str">
+        <v>No</v>
+      </c>
+      <c r="I69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B70" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Primary Care (Office)</v>
+      </c>
+      <c r="E70" t="str">
+        <v>$40.00 copay/office visit (30% coinsurance for other outpatient services)</v>
+      </c>
+      <c r="F70">
+        <v>40</v>
+      </c>
+      <c r="H70" t="str">
+        <v>No</v>
+      </c>
+      <c r="I70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B71" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C71">
+        <v>2</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Specialist (Office)</v>
+      </c>
+      <c r="E71" t="str">
+        <v>$80.00</v>
+      </c>
+      <c r="F71">
+        <v>80</v>
+      </c>
+      <c r="H71" t="str">
+        <v>No</v>
+      </c>
+      <c r="I71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B72" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Preventive Care / Screening / Immunization</v>
+      </c>
+      <c r="E72" t="str">
+        <v>No charge</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="H72" t="str">
+        <v>No</v>
+      </c>
+      <c r="I72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B73" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C73">
+        <v>4</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Diagnostic Tests (X-Ray/Lab)</v>
+      </c>
+      <c r="E73" t="str">
+        <v>30%</v>
+      </c>
+      <c r="G73">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H73" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B74" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C74">
+        <v>5</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Imaging (CT/PET/MRI)</v>
+      </c>
+      <c r="E74" t="str">
+        <v>30% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G74">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H74" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B75" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C75">
+        <v>6</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Tier 1 Rx (Generic, Retail)</v>
+      </c>
+      <c r="E75" t="str">
+        <v>$20.00</v>
+      </c>
+      <c r="F75">
+        <v>20</v>
+      </c>
+      <c r="H75" t="str">
+        <v>No</v>
+      </c>
+      <c r="I75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B76" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C76">
+        <v>7</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Tier 1 Rx (Generic, Mail Order)</v>
+      </c>
+      <c r="E76" t="str">
+        <v>$50.00</v>
+      </c>
+      <c r="F76">
+        <v>50</v>
+      </c>
+      <c r="H76" t="str">
+        <v>No</v>
+      </c>
+      <c r="I76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B77" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C77">
+        <v>8</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Tier 2 Rx (Preferred Brand, Retail)</v>
+      </c>
+      <c r="E77" t="str">
+        <v>$50.00</v>
+      </c>
+      <c r="F77">
+        <v>50</v>
+      </c>
+      <c r="H77" t="str">
+        <v>No</v>
+      </c>
+      <c r="I77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B78" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C78">
+        <v>9</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Tier 2 Rx (Preferred Brand, Mail Order)</v>
+      </c>
+      <c r="E78" t="str">
+        <v>$125.00</v>
+      </c>
+      <c r="F78">
+        <v>125</v>
+      </c>
+      <c r="H78" t="str">
+        <v>No</v>
+      </c>
+      <c r="I78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B79" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C79">
+        <v>10</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Tier 3 Rx (Non-Preferred Brand, Retail)</v>
+      </c>
+      <c r="E79" t="str">
+        <v>$100.00</v>
+      </c>
+      <c r="F79">
+        <v>100</v>
+      </c>
+      <c r="H79" t="str">
+        <v>No</v>
+      </c>
+      <c r="I79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B80" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C80">
+        <v>11</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Tier 3 Rx (Non-Preferred Brand, Mail Order)</v>
+      </c>
+      <c r="E80" t="str">
+        <v>$250.00</v>
+      </c>
+      <c r="F80">
+        <v>250</v>
+      </c>
+      <c r="H80" t="str">
+        <v>No</v>
+      </c>
+      <c r="I80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B81" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C81">
+        <v>12</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Tier 4 Rx (Specialty)</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Not covered</v>
+      </c>
+      <c r="H81" t="str">
+        <v>No</v>
+      </c>
+      <c r="I81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B82" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C82">
+        <v>13</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Outpatient Surgery - Facility Fee</v>
+      </c>
+      <c r="E82" t="str">
+        <v>30% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G82">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B83" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C83">
+        <v>14</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Outpatient Surgery - Physician/Surgeon Fees</v>
+      </c>
+      <c r="E83" t="str">
+        <v>30% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G83">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B84" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C84">
+        <v>15</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Emergency Room</v>
+      </c>
+      <c r="E84" t="str">
+        <v>30% coinsurance; non-emergency use reduces covered charges by 25%</v>
+      </c>
+      <c r="G84">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B85" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C85">
+        <v>16</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Emergency Medical Transportation</v>
+      </c>
+      <c r="E85" t="str">
+        <v>30%</v>
+      </c>
+      <c r="G85">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H85" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B86" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C86">
+        <v>17</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Urgent Care</v>
+      </c>
+      <c r="E86" t="str">
+        <v>$100.00</v>
+      </c>
+      <c r="F86">
+        <v>100</v>
+      </c>
+      <c r="H86" t="str">
+        <v>No</v>
+      </c>
+      <c r="I86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B87" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C87">
+        <v>18</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Inpatient Facility</v>
+      </c>
+      <c r="E87" t="str">
+        <v>30% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G87">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H87" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B88" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C88">
+        <v>19</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Hospital - Physician/Surgeon Fees</v>
+      </c>
+      <c r="E88" t="str">
+        <v>30% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G88">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H88" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B89" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C89">
+        <v>20</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Mental/Behavioral Health - Outpatient</v>
+      </c>
+      <c r="E89" t="str">
+        <v>50% coinsurance; preauthorization required; 30 visit/year limit</v>
+      </c>
+      <c r="G89">
+        <v>0.5</v>
+      </c>
+      <c r="H89" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B90" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C90">
+        <v>21</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Mental/Behavioral Health - Inpatient</v>
+      </c>
+      <c r="E90" t="str">
+        <v>50% coinsurance; preauthorization required; 30 day/year limit</v>
+      </c>
+      <c r="G90">
+        <v>0.5</v>
+      </c>
+      <c r="H90" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B91" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C91">
+        <v>22</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Maternity - Office Visits</v>
+      </c>
+      <c r="E91" t="str">
+        <v>$40.00 copay/office visit (30% coinsurance for other outpatient services); no cost sharing for preventive services</v>
+      </c>
+      <c r="F91">
+        <v>40</v>
+      </c>
+      <c r="H91" t="str">
+        <v>No</v>
+      </c>
+      <c r="I91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B92" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C92">
+        <v>23</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Maternity - Delivery, Professional</v>
+      </c>
+      <c r="E92" t="str">
+        <v>30% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G92">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B93" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C93">
+        <v>24</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Maternity - Delivery, Facility</v>
+      </c>
+      <c r="E93" t="str">
+        <v>30% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G93">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B94" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C94">
+        <v>25</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Home Health Care</v>
+      </c>
+      <c r="E94" t="str">
+        <v>30% coinsurance; preauthorization required; 45 visit/year limit</v>
+      </c>
+      <c r="G94">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B95" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C95">
+        <v>26</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Rehabilitation Services</v>
+      </c>
+      <c r="E95" t="str">
+        <v>30% coinsurance; preauthorization required (inpatient); inpatient 30 day/year limit combined with skilled nursing; outpatient 30 visit/year limit</v>
+      </c>
+      <c r="G95">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B96" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C96">
+        <v>27</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Habilitation Services</v>
+      </c>
+      <c r="E96" t="str">
+        <v>30% coinsurance; same combined limits as rehabilitation services</v>
+      </c>
+      <c r="G96">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B97" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C97">
+        <v>28</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Skilled Nursing Care</v>
+      </c>
+      <c r="E97" t="str">
+        <v>30% coinsurance; preauthorization required; 30 day/year limit combined with inpatient rehabilitation</v>
+      </c>
+      <c r="G97">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B98" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C98">
+        <v>29</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Durable Medical Equipment</v>
+      </c>
+      <c r="E98" t="str">
+        <v>30% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G98">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B99" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C99">
+        <v>30</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Hospice Services</v>
+      </c>
+      <c r="E99" t="str">
+        <v>30% coinsurance; preauthorization required; 180 day/year limit</v>
+      </c>
+      <c r="G99">
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B100" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C100">
+        <v>31</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Children's Eye Exam</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Not covered</v>
+      </c>
+      <c r="H100" t="str">
+        <v>No</v>
+      </c>
+      <c r="I100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B101" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C101">
+        <v>32</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Children's Glasses</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Not covered</v>
+      </c>
+      <c r="H101" t="str">
+        <v>No</v>
+      </c>
+      <c r="I101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B102" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C102">
+        <v>33</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Children's Dental Check-Up</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Not covered</v>
+      </c>
+      <c r="H102" t="str">
+        <v>No</v>
+      </c>
+      <c r="I102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>OPTIMYL-3</v>
+      </c>
+      <c r="B103" t="str">
+        <v>OPTIMYL PLAN 3</v>
+      </c>
+      <c r="C103">
+        <v>34</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Telemedicine (Physician + Behavioral Health)</v>
+      </c>
+      <c r="E103" t="str">
+        <v>Included, per the carrier's proposal summary</v>
+      </c>
+      <c r="H103" t="str">
+        <v>No</v>
+      </c>
+      <c r="I103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
         <v>OPTIMYL-4</v>
       </c>
-      <c r="B45" t="str">
+      <c r="B104" t="str">
         <v>OPTIMYL PLAN 4</v>
       </c>
-      <c r="C45">
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Primary Care (Office)</v>
+      </c>
+      <c r="E104" t="str">
+        <v>$40.00 copay/office visit (50% coinsurance for other outpatient services)</v>
+      </c>
+      <c r="F104">
+        <v>40</v>
+      </c>
+      <c r="H104" t="str">
+        <v>No</v>
+      </c>
+      <c r="I104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B105" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Specialist (Office)</v>
+      </c>
+      <c r="E105" t="str">
+        <v>$80.00</v>
+      </c>
+      <c r="F105">
+        <v>80</v>
+      </c>
+      <c r="H105" t="str">
+        <v>No</v>
+      </c>
+      <c r="I105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B106" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C106">
+        <v>3</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Preventive Care / Screening / Immunization</v>
+      </c>
+      <c r="E106" t="str">
+        <v>No charge</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="H106" t="str">
+        <v>No</v>
+      </c>
+      <c r="I106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B107" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C107">
+        <v>4</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Diagnostic Tests (X-Ray/Lab)</v>
+      </c>
+      <c r="E107" t="str">
+        <v>50%</v>
+      </c>
+      <c r="G107">
+        <v>0.5</v>
+      </c>
+      <c r="H107" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B108" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C108">
+        <v>5</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Imaging (CT/PET/MRI)</v>
+      </c>
+      <c r="E108" t="str">
+        <v>50% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G108">
+        <v>0.5</v>
+      </c>
+      <c r="H108" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B109" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C109">
+        <v>6</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Tier 1 Rx (Generic, Retail)</v>
+      </c>
+      <c r="E109" t="str">
+        <v>$20.00</v>
+      </c>
+      <c r="F109">
+        <v>20</v>
+      </c>
+      <c r="H109" t="str">
+        <v>No</v>
+      </c>
+      <c r="I109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B110" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C110">
+        <v>7</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Tier 1 Rx (Generic, Mail Order)</v>
+      </c>
+      <c r="E110" t="str">
+        <v>$50.00</v>
+      </c>
+      <c r="F110">
+        <v>50</v>
+      </c>
+      <c r="H110" t="str">
+        <v>No</v>
+      </c>
+      <c r="I110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B111" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C111">
+        <v>8</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Tier 2 Rx (Preferred Brand, Retail)</v>
+      </c>
+      <c r="E111" t="str">
+        <v>$50.00</v>
+      </c>
+      <c r="F111">
+        <v>50</v>
+      </c>
+      <c r="H111" t="str">
+        <v>No</v>
+      </c>
+      <c r="I111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B112" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C112">
+        <v>9</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Tier 2 Rx (Preferred Brand, Mail Order)</v>
+      </c>
+      <c r="E112" t="str">
+        <v>$125.00</v>
+      </c>
+      <c r="F112">
+        <v>125</v>
+      </c>
+      <c r="H112" t="str">
+        <v>No</v>
+      </c>
+      <c r="I112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B113" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C113">
+        <v>10</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Tier 3 Rx (Non-Preferred Brand, Retail)</v>
+      </c>
+      <c r="E113" t="str">
+        <v>$100.00</v>
+      </c>
+      <c r="F113">
+        <v>100</v>
+      </c>
+      <c r="H113" t="str">
+        <v>No</v>
+      </c>
+      <c r="I113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B114" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C114">
         <v>11</v>
       </c>
-      <c r="D45" t="str">
+      <c r="D114" t="str">
+        <v>Tier 3 Rx (Non-Preferred Brand, Mail Order)</v>
+      </c>
+      <c r="E114" t="str">
+        <v>$250.00</v>
+      </c>
+      <c r="F114">
+        <v>250</v>
+      </c>
+      <c r="H114" t="str">
+        <v>No</v>
+      </c>
+      <c r="I114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B115" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C115">
+        <v>12</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Tier 4 Rx (Specialty)</v>
+      </c>
+      <c r="E115" t="str">
+        <v>Not covered</v>
+      </c>
+      <c r="H115" t="str">
+        <v>No</v>
+      </c>
+      <c r="I115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B116" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C116">
+        <v>13</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Outpatient Surgery - Facility Fee</v>
+      </c>
+      <c r="E116" t="str">
+        <v>50% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G116">
+        <v>0.5</v>
+      </c>
+      <c r="H116" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I116">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B117" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C117">
+        <v>14</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Outpatient Surgery - Physician/Surgeon Fees</v>
+      </c>
+      <c r="E117" t="str">
+        <v>50% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G117">
+        <v>0.5</v>
+      </c>
+      <c r="H117" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B118" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C118">
+        <v>15</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Emergency Room</v>
+      </c>
+      <c r="E118" t="str">
+        <v>50% coinsurance; non-emergency use reduces covered charges by 25%</v>
+      </c>
+      <c r="G118">
+        <v>0.5</v>
+      </c>
+      <c r="H118" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I118">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B119" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C119">
+        <v>16</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Emergency Medical Transportation</v>
+      </c>
+      <c r="E119" t="str">
+        <v>50%</v>
+      </c>
+      <c r="G119">
+        <v>0.5</v>
+      </c>
+      <c r="H119" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I119">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B120" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C120">
+        <v>17</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Urgent Care</v>
+      </c>
+      <c r="E120" t="str">
+        <v>$100.00</v>
+      </c>
+      <c r="F120">
+        <v>100</v>
+      </c>
+      <c r="H120" t="str">
+        <v>No</v>
+      </c>
+      <c r="I120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B121" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C121">
+        <v>18</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Inpatient Facility</v>
+      </c>
+      <c r="E121" t="str">
+        <v>50% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G121">
+        <v>0.5</v>
+      </c>
+      <c r="H121" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B122" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C122">
+        <v>19</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Hospital - Physician/Surgeon Fees</v>
+      </c>
+      <c r="E122" t="str">
+        <v>50% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G122">
+        <v>0.5</v>
+      </c>
+      <c r="H122" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B123" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C123">
+        <v>20</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Mental/Behavioral Health - Outpatient</v>
+      </c>
+      <c r="E123" t="str">
+        <v>50% coinsurance; preauthorization required; 30 visit/year limit</v>
+      </c>
+      <c r="G123">
+        <v>0.5</v>
+      </c>
+      <c r="H123" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B124" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C124">
+        <v>21</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Mental/Behavioral Health - Inpatient</v>
+      </c>
+      <c r="E124" t="str">
+        <v>50% coinsurance; preauthorization required; 30 day/year limit</v>
+      </c>
+      <c r="G124">
+        <v>0.5</v>
+      </c>
+      <c r="H124" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B125" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C125">
+        <v>22</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Maternity - Office Visits</v>
+      </c>
+      <c r="E125" t="str">
+        <v>$40.00 copay/office visit (50% coinsurance for other outpatient services); no cost sharing for preventive services</v>
+      </c>
+      <c r="F125">
+        <v>40</v>
+      </c>
+      <c r="H125" t="str">
+        <v>No</v>
+      </c>
+      <c r="I125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B126" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C126">
+        <v>23</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Maternity - Delivery, Professional</v>
+      </c>
+      <c r="E126" t="str">
+        <v>50% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G126">
+        <v>0.5</v>
+      </c>
+      <c r="H126" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I126">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B127" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C127">
+        <v>24</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Maternity - Delivery, Facility</v>
+      </c>
+      <c r="E127" t="str">
+        <v>50% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G127">
+        <v>0.5</v>
+      </c>
+      <c r="H127" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B128" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C128">
+        <v>25</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Home Health Care</v>
+      </c>
+      <c r="E128" t="str">
+        <v>50% coinsurance; preauthorization required; 45 visit/year limit</v>
+      </c>
+      <c r="G128">
+        <v>0.5</v>
+      </c>
+      <c r="H128" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I128">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B129" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C129">
+        <v>26</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Rehabilitation Services</v>
+      </c>
+      <c r="E129" t="str">
+        <v>50% coinsurance; preauthorization required (inpatient); inpatient 30 day/year limit combined with skilled nursing; outpatient 30 visit/year limit</v>
+      </c>
+      <c r="G129">
+        <v>0.5</v>
+      </c>
+      <c r="H129" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I129">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B130" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C130">
+        <v>27</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Habilitation Services</v>
+      </c>
+      <c r="E130" t="str">
+        <v>50% coinsurance; same combined limits as rehabilitation services</v>
+      </c>
+      <c r="G130">
+        <v>0.5</v>
+      </c>
+      <c r="H130" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I130">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B131" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C131">
+        <v>28</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Skilled Nursing Care</v>
+      </c>
+      <c r="E131" t="str">
+        <v>50% coinsurance; preauthorization required; 30 day/year limit combined with inpatient rehabilitation</v>
+      </c>
+      <c r="G131">
+        <v>0.5</v>
+      </c>
+      <c r="H131" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B132" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C132">
+        <v>29</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Durable Medical Equipment</v>
+      </c>
+      <c r="E132" t="str">
+        <v>50% coinsurance; preauthorization required</v>
+      </c>
+      <c r="G132">
+        <v>0.5</v>
+      </c>
+      <c r="H132" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I132">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B133" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C133">
+        <v>30</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Hospice Services</v>
+      </c>
+      <c r="E133" t="str">
+        <v>50% coinsurance; preauthorization required; 180 day/year limit</v>
+      </c>
+      <c r="G133">
+        <v>0.5</v>
+      </c>
+      <c r="H133" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I133">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B134" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C134">
+        <v>31</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Children's Eye Exam</v>
+      </c>
+      <c r="E134" t="str">
+        <v>Not covered</v>
+      </c>
+      <c r="H134" t="str">
+        <v>No</v>
+      </c>
+      <c r="I134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B135" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C135">
+        <v>32</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Children's Glasses</v>
+      </c>
+      <c r="E135" t="str">
+        <v>Not covered</v>
+      </c>
+      <c r="H135" t="str">
+        <v>No</v>
+      </c>
+      <c r="I135">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B136" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C136">
+        <v>33</v>
+      </c>
+      <c r="D136" t="str">
+        <v>Children's Dental Check-Up</v>
+      </c>
+      <c r="E136" t="str">
+        <v>Not covered</v>
+      </c>
+      <c r="H136" t="str">
+        <v>No</v>
+      </c>
+      <c r="I136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>OPTIMYL-4</v>
+      </c>
+      <c r="B137" t="str">
+        <v>OPTIMYL PLAN 4</v>
+      </c>
+      <c r="C137">
+        <v>34</v>
+      </c>
+      <c r="D137" t="str">
         <v>Telemedicine (Physician + Behavioral Health)</v>
       </c>
-      <c r="E45" t="str">
-        <v>Included</v>
-      </c>
-      <c r="H45" t="str">
-        <v>No</v>
-      </c>
-      <c r="I45">
+      <c r="E137" t="str">
+        <v>Included, per the carrier's proposal summary</v>
+      </c>
+      <c r="H137" t="str">
+        <v>No</v>
+      </c>
+      <c r="I137">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I137"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1745,7 +4101,7 @@
         <v>Source</v>
       </c>
       <c r="B2" t="str">
-        <v>"Re: Optimyl Benefits" proposal email from Brody Gibbs (Optimyl Benefits), St Clair Eye PLLC, Proposal ID 0Q0Uv000003MbSEKA0, effective 01/01/2027. Only plan design fields are included; rates are group-specific and live on each group's own uploaded proposal.</v>
+        <v>"Re: Optimyl Benefits" proposal email from Brody Gibbs (Optimyl Benefits): the carrier's Proposal Summary (deductibles, OOP maxes, coinsurance, monthly costs) plus its 4 per-plan Summaries of Benefits and Coverage / SBCs (the full standard ACA benefit categories). St Clair Eye PLLC, Proposal ID 0Q0Uv000003MbSEKA0, effective 01/01/2027. Only plan design fields are included; rates are group-specific and live on each group's own uploaded proposal.</v>
       </c>
     </row>
     <row r="3">
@@ -1753,7 +4109,7 @@
         <v>Program</v>
       </c>
       <c r="B3" t="str">
-        <v>Optimyl Benefits Self-Funded Program: reference-based pricing (RBP), network "RBP Full". Stop Loss is underwritten by The North River Insurance Company or Gerber Life Insurance Company. Pharmacy benefit manager: CVS (closed formulary).</v>
+        <v>Optimyl Benefits Self-Funded Program: reference-based pricing (RBP); the SBCs describe it as an Indemnity plan with no provider network ("you can receive covered services from any provider"), consistent with RBP - no referrals needed. Pharmacy benefit manager: CVS Caremark (closed formulary, generic-first, penalty for a brand fill when a generic exists).</v>
       </c>
     </row>
     <row r="4">
@@ -1785,15 +4141,15 @@
         <v>Coinsurance</v>
       </c>
       <c r="B7" t="str">
-        <v>The proposal states the plan's paid share (e.g. 80%). cost_share_percent here stores the member's share after deductible (100% minus that), consistent with the Angle Health catalogue's convention.</v>
+        <v>The proposal states the plan's paid share (e.g. 80%). cost_share_percent here stores the member's share after deductible (100% minus that), consistent with the Angle Health catalogue's convention. Mental/behavioral health/substance abuse is a fixed 50% member coinsurance on every plan regardless of the plan's own rate, per every SBC.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Inpatient Facility</v>
+        <v>Prescription drugs</v>
       </c>
       <c r="B8" t="str">
-        <v>Not printed as its own line on the proposal's summary grid; given the same deductible-then-coinsurance cost share the grid states explicitly for Emergency Room and X-ray/Lab, since that is the RBP program's default cost share for a covered service with no separate copay.</v>
+        <v>Each Rx tier has a retail figure (30-day supply) and a separate, higher mail-order figure (31-90 day supply) per the SBCs; the retail figure is what the six-line card summary shows (matched first by service_order), the mail-order figure is a second, later line under the same tier wording so it is stored but does not change the summary.</v>
       </c>
     </row>
     <row r="9">
@@ -1809,15 +4165,15 @@
         <v>Out-of-network</v>
       </c>
       <c r="B10" t="str">
-        <v>The proposal gives no separate out-of-network figures (RBP has no traditional network split), so the oon_* columns are blank.</v>
+        <v>The SBCs state this plan uses no provider network at all (pay the same regardless of provider), so there are no separate out-of-network figures; the oon_* columns are blank.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Specialty Rx</v>
+        <v>Specialty Rx and other exclusions</v>
       </c>
       <c r="B11" t="str">
-        <v>Specialty drugs are not covered under any of the 4 plans per the proposal's Terms page.</v>
+        <v>Specialty drugs, adult dental/vision/hearing, infertility treatment, cosmetic/experimental care, and children's vision/dental are not covered on any of the 4 plans, per every SBC's exclusions list and the proposal's Terms page.</v>
       </c>
     </row>
   </sheetData>
